--- a/forms/trg/Formulir_TRG_proagritech.xlsx
+++ b/forms/trg/Formulir_TRG_proagritech.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
+          <t>Data TRG ini relatif lengkap. Mohon periksa dan lengkapi mitra serta riset terbaik.</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Abdul Azis, STP, M.Si</t>
+          <t>Prof. Dr. Iqbal, STP., M.Si., IPM</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Mechanization; Instrumentation and Control; Precision Farming; Smart Farming</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Agricultural Mechanical Engineering</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -938,10 +938,14 @@
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6054844</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="n"/>
+          <t>5979933</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>56607208000</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -954,17 +958,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Tahir Sapsal, STP, M.Si</t>
+          <t>Dr. Abdul Azis, STP, M.Si</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Mechanical Engineering</t>
+          <t>Agricultural Mechanization; Instrumentation and Control; Precision Farming; Smart Farming</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -976,21 +980,13 @@
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-8830-1235</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6024504</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57200306629</t>
-        </is>
-      </c>
+          <t>6054844</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1003,17 +999,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Husnul Mubarak, STP., M.Si</t>
+          <t>Muhammad Tahir Sapsal, STP, M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Water Resources Management</t>
+          <t>Agricultural Mechanical Engineering</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -1027,17 +1023,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1404-2960</t>
+          <t>0000-0001-8830-1235</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6736138</t>
+          <t>6024504</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57217144732</t>
+          <t>57200306629</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1052,17 +1048,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Ir. Samsuar, STP., M.Si</t>
+          <t>Husnul Mubarak, STP., M.Si</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Soil, Water and Environmental Engineering</t>
+          <t>Water Resources Management</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -1074,9 +1070,21 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-1404-2960</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>6736138</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57217144732</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1089,17 +1097,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Syahrial Sabaniah, STP., MT</t>
+          <t>Ir. Samsuar, STP., M.Si</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Instrumentation and Control</t>
+          <t>Soil, Water and Environmental Engineering</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -1126,22 +1134,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Wanrat Abdullakasim, PhD</t>
+          <t>Syahrial Sabaniah, STP., MT</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Science</t>
+          <t>Instrumentation and Control</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Kasetsart University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1163,22 +1171,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Arcanjo De Jesus</t>
+          <t>Wanrat Abdullakasim, PhD</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Mechanical Engineering</t>
+          <t>Agricultural Science</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Universidade Orental Timor Lorosa'e</t>
+          <t>Kasetsart University</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1200,22 +1208,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Andi Baso Kresna, STP, M.TP</t>
+          <t>Arcanjo De Jesus</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Agriculture machinery</t>
+          <t>Agricultural Mechanical Engineering</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Batangkaluku Agricultural Training Centre</t>
+          <t>Universidade Orental Timor Lorosa'e</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1237,22 +1245,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Kasmira, S.TP</t>
+          <t>Andi Baso Kresna, STP, M.TP</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Mechanical Engineering</t>
+          <t>Agriculture machinery</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Batangkaluku Agricultural Training Centre</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1261,11 +1269,7 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>57297345800</t>
-        </is>
-      </c>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1278,17 +1282,17 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Aqid Mukhtar, STP</t>
+          <t>Kasmira, S.TP</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Instrumentation and Control</t>
+          <t>Agricultural Mechanical Engineering</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -1302,7 +1306,11 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>57297345800</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1315,17 +1323,17 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Yusuf Arif, STP</t>
+          <t>Aqid Mukhtar, STP</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Mechanical Engineering</t>
+          <t>Instrumentation and Control</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
@@ -1352,17 +1360,17 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Sitti Nurhidayatullah Rahim, STP</t>
+          <t>Muhammad Yusuf Arif, STP</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>GIS dan Remote Sensing</t>
+          <t>Agricultural Mechanical Engineering</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -1389,17 +1397,17 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Nurul chintia, STP</t>
+          <t>Sitti Nurhidayatullah Rahim, STP</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Water Resources Management</t>
+          <t>GIS dan Remote Sensing</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -1426,17 +1434,17 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Zubaer, STP</t>
+          <t>Nurul chintia, STP</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Agriculture machinery</t>
+          <t>Water Resources Management</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1463,17 +1471,17 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Sulhikma Ramadhan, STP</t>
+          <t>Zubaer, STP</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Agricultural Mechanical Engineering</t>
+          <t>Agriculture machinery</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -1498,10 +1506,26 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Sulhikma Ramadhan, STP</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>The Appropriate Agricultural Technology Research Group (proAgriTech) is dedicated to advancing the development of modern and affordable agricultural tools tailored to farmers' needs. By integrating cutting-edge technologies in instrumentation, control systems, and automation, we aim to enhance the productivity and efficiency of the agricultural sector. Our multidisciplinary approach encourages collaboration with farmers, industry partners, and academic institutions, fostering the rapid adoption of innovative solutions in the field. At the heart of our mission is the commitment to improving farmers' welfare by providing practical and sustainable technologies. With research sub-themes focused on farm machinery and agricultural automation, proAgriTech is at the forefront of appropriate technology development that aligns with both local challenges and global advancements.</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -1509,7 +1533,11 @@
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1698,15 +1726,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
